--- a/results/2019_mf3.xlsx
+++ b/results/2019_mf3.xlsx
@@ -528,34 +528,34 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.031</v>
+        <v>0.038</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.182</v>
+        <v>0.133</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.457</v>
+        <v>0.36</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.601</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.399</v>
+        <v>0.435</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.056</v>
+        <v>0.05</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.109</v>
+        <v>0.089</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.275</v>
+        <v>0.23</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -673,28 +673,28 @@
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.667</v>
+        <v>0.25</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.778</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.828</v>
+        <v>0.722</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.001</v>
+        <v>0.023</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.115</v>
+        <v>0.164</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.276</v>
+        <v>0.244</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.553</v>
+        <v>0.408</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the respiratory system</t>
+          <t>Diseases of the skin and subcutaneous tissue</t>
         </is>
       </c>
     </row>
@@ -732,22 +732,22 @@
         <v>0</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.833</v>
+        <v>0.556</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.065</v>
+        <v>0.034</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.331</v>
+        <v>0.242</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>0</v>
@@ -760,7 +760,7 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the blood and blood-forming organs and certain disorders involving the immune mechanism</t>
+          <t>Diseases of the respiratory system</t>
         </is>
       </c>
     </row>
@@ -779,28 +779,28 @@
         <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.143</v>
+        <v>0.167</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.214</v>
+        <v>0.25</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.414</v>
+        <v>0.516</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.013</v>
+        <v>0.063</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.101</v>
+        <v>0.156</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.159</v>
+        <v>0.2</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.306</v>
+        <v>0.332</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Endocrine, nutritional and metabolic diseases</t>
+          <t>Diseases of the genitourinary system</t>
         </is>
       </c>
     </row>
@@ -832,28 +832,28 @@
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.04</v>
+        <v>0.016</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.272</v>
+        <v>0.258</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.522</v>
+        <v>0.45</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.634</v>
+        <v>0.599</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.099</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.174</v>
+        <v>0.146</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.348</v>
+        <v>0.314</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the circulatory system</t>
+          <t>Neoplasms</t>
         </is>
       </c>
     </row>
@@ -882,31 +882,31 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.25</v>
+        <v>0.162</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.75</v>
+        <v>0.427</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.633</v>
+        <v>0.581</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.003</v>
+        <v>0.023</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1</v>
+        <v>0.047</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.171</v>
+        <v>0.09</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.364</v>
+        <v>0.247</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>0</v>
@@ -919,7 +919,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the skin and subcutaneous tissue</t>
+          <t>Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -941,25 +941,25 @@
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.125</v>
+        <v>0.061</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.312</v>
+        <v>0.328</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.616</v>
+        <v>0.578</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.073</v>
+        <v>0.035</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.245</v>
+        <v>0.197</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the digestive system</t>
+          <t>Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
@@ -988,31 +988,31 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0.489</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0.065</v>
-      </c>
       <c r="J8" s="4" t="n">
-        <v>0.093</v>
+        <v>0.054</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.228</v>
+        <v>0.163</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Mental and behavioural disorders</t>
+          <t>Diseases of the nervous system</t>
         </is>
       </c>
     </row>
@@ -1047,25 +1047,25 @@
         <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.337</v>
+        <v>0.333</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.578</v>
+        <v>0.497</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.033</v>
+        <v>0.021</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.183</v>
+        <v>0.152</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>0</v>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the genitourinary system</t>
+          <t>Diseases of the blood and blood-forming organs and certain disorders involving the immune mechanism</t>
         </is>
       </c>
     </row>
@@ -1097,28 +1097,28 @@
         <v>0</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.541</v>
+        <v>0.482</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.133</v>
+        <v>0.002</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.262</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the nervous system</t>
+          <t>Diseases of the musculoskeletal system and connective tissue</t>
         </is>
       </c>
     </row>
@@ -1150,28 +1150,28 @@
         <v>0</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.303</v>
+        <v>0.143</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.535</v>
+        <v>0.436</v>
       </c>
       <c r="H11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
         <v>0.002</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>0.017</v>
-      </c>
       <c r="J11" s="6" t="n">
-        <v>0.042</v>
+        <v>0.016</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.178</v>
+        <v>0.106</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>0</v>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>Neoplasms</t>
+          <t>Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
@@ -1206,25 +1206,25 @@
         <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.333</v>
+        <v>0.062</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.333</v>
+        <v>0.188</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.532</v>
+        <v>0.387</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.093</v>
+        <v>0.023</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.258</v>
+        <v>0.104</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the musculoskeletal system and connective tissue</t>
+          <t>Diseases of the digestive system</t>
         </is>
       </c>
     </row>
@@ -1357,31 +1357,31 @@
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0.16</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.661</v>
+        <v>0.524</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.34</v>
+        <v>0.476</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.093</v>
+        <v>0.057</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.144</v>
+        <v>0.102</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.322</v>
+        <v>0.237</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
@@ -1421,28 +1421,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.222</v>
+        <v>0.444</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.525</v>
+        <v>0.706</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.475</v>
+        <v>0.294</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.006</v>
+        <v>0.112</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.035</v>
+        <v>0.205</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.166</v>
+        <v>0.393</v>
       </c>
       <c r="M3" s="6" t="n">
         <v>0</v>
@@ -1482,28 +1482,28 @@
         <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.14</v>
+        <v>0.931</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.86</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.006</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -1549,10 +1549,10 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.62</v>
+        <v>0.29</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.129</v>
+        <v>0.018</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>0</v>
@@ -1601,31 +1601,31 @@
         <v>0</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.098</v>
+        <v>0.082</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.213</v>
+        <v>0.328</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.438</v>
+        <v>0.525</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.475</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.012</v>
+        <v>0.033</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.037</v>
+        <v>0.06</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.138</v>
+        <v>0.187</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
@@ -1665,28 +1665,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>0.667</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.644</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.307</v>
+        <v>0.356</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.002</v>
+        <v>0.168</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.032</v>
+        <v>0.278</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.259</v>
+        <v>0.47</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>0</v>
@@ -1723,31 +1723,31 @@
         <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.105</v>
+        <v>0.158</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.474</v>
+        <v>0.263</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.656</v>
+        <v>0.514</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.344</v>
+        <v>0.486</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.027</v>
+        <v>0.062</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.083</v>
+        <v>0.097</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.282</v>
+        <v>0.209</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>0</v>
@@ -1790,25 +1790,25 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.546</v>
+        <v>0.659</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.454</v>
+        <v>0.342</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.005</v>
+        <v>0.091</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.123</v>
+        <v>0.306</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>0</v>
@@ -1854,22 +1854,22 @@
         <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.193</v>
+        <v>0.171</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.045</v>
+        <v>0.064</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.356</v>
+        <v>0.402</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>0</v>
@@ -1912,25 +1912,25 @@
         <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.88</v>
+        <v>0.352</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.12</v>
+        <v>0.648</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.528</v>
+        <v>0.027</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>0</v>
@@ -1973,13 +1973,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.413</v>
+        <v>0.311</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.586</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>0</v>
@@ -1988,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.108</v>
+        <v>0.028</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>0</v>
@@ -2028,31 +2028,31 @@
         <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>0.286</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>0.429</v>
-      </c>
       <c r="G13" s="6" t="n">
-        <v>0.715</v>
+        <v>0.477</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.285</v>
+        <v>0.523</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.194</v>
+        <v>0.004</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.275</v>
+        <v>0.031</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.423</v>
+        <v>0.157</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>0</v>
@@ -2095,25 +2095,25 @@
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.395</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.434</v>
+        <v>0.605</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.189</v>
+        <v>0.054</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>0</v>
@@ -2153,28 +2153,28 @@
         <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.107</v>
+        <v>0.179</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.357</v>
+        <v>0.393</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.517</v>
+        <v>0.523</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.484</v>
+        <v>0.477</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.054</v>
+        <v>0.044</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.219</v>
+        <v>0.228</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>0</v>
@@ -2208,34 +2208,34 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0.125</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.642</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.358</v>
+        <v>0.443</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.125</v>
+        <v>0.006</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.152</v>
+        <v>0.036</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.306</v>
+        <v>0.194</v>
       </c>
       <c r="M16" s="4" t="n">
         <v>0</v>
@@ -2278,13 +2278,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.701</v>
+        <v>0.699</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.299</v>
+        <v>0.302</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0.008</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.201</v>
+        <v>0.198</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>0</v>
@@ -2333,31 +2333,31 @@
         <v>0</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.624</v>
+        <v>0.518</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.376</v>
+        <v>0.482</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.147</v>
+        <v>0.002</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.206</v>
+        <v>0.017</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.32</v>
+        <v>0.158</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>0</v>
@@ -2400,25 +2400,25 @@
         <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.286</v>
+        <v>0.571</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.449</v>
+        <v>0.594</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.551</v>
+        <v>0.406</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.094</v>
+        <v>0.206</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>0</v>
@@ -2458,28 +2458,28 @@
         <v>0</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.948</v>
+        <v>0.431</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.052</v>
+        <v>0.569</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.433</v>
+        <v>0</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.758</v>
+        <v>0.044</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>0</v>
@@ -2522,25 +2522,25 @@
         <v>0</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.8</v>
+        <v>0.228</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.2</v>
+        <v>0.772</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.346</v>
+        <v>0.017</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>0</v>
@@ -2577,31 +2577,31 @@
         <v>0</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0.25</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.515</v>
+        <v>0.378</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.485</v>
+        <v>0.622</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.205</v>
+        <v>0.006</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.277</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="M22" s="4" t="n">
         <v>0</v>
@@ -2641,28 +2641,28 @@
         <v>0</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.125</v>
+        <v>0.375</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.418</v>
+        <v>0.552</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.582</v>
+        <v>0.448</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.004</v>
+        <v>0.153</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.077</v>
+        <v>0.274</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.317</v>
+        <v>0.606</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.394</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -2720,10 +2720,10 @@
         <v>0</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.051</v>
+        <v>0.132</v>
       </c>
       <c r="M24" s="4" t="n">
         <v>0</v>
@@ -2760,31 +2760,31 @@
         <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.342</v>
+        <v>0.645</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.658</v>
+        <v>0.355</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.236</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.243</v>
+        <v>0.013</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.252</v>
+        <v>0.187</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>0</v>
@@ -2824,28 +2824,28 @@
         <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.446</v>
+        <v>0.724</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.554</v>
+        <v>0.277</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.001</v>
+        <v>0.203</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.075</v>
+        <v>0.404</v>
       </c>
       <c r="M26" s="4" t="n">
         <v>0</v>
@@ -2879,34 +2879,34 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.2</v>
+        <v>0.067</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.768</v>
+        <v>0.714</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.232</v>
+        <v>0.286</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.049</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.208</v>
+        <v>0.096</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.286</v>
+        <v>0.165</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.457</v>
+        <v>0.381</v>
       </c>
       <c r="M27" s="6" t="n">
         <v>0</v>
@@ -2943,31 +2943,31 @@
         <v>0</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.636</v>
+        <v>0.598</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.364</v>
+        <v>0.402</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.052</v>
+        <v>0.047</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.117</v>
+        <v>0.113</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.317</v>
+        <v>0.281</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.178</v>
+        <v>0.344</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.822</v>
+        <v>0.656</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>0</v>
@@ -3065,31 +3065,31 @@
         <v>0</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>0.111</v>
       </c>
       <c r="F30" s="4" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H30" s="3" t="n">
         <v>0.444</v>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>0.398</v>
-      </c>
       <c r="I30" s="4" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.024</v>
+        <v>0.106</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.065</v>
+        <v>0.125</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.24</v>
+        <v>0.237</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>0</v>
@@ -3129,28 +3129,28 @@
         <v>0.038</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.192</v>
+        <v>0.154</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>0.423</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.543</v>
+        <v>0.478</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.457</v>
+        <v>0.522</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.056</v>
+        <v>0.053</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.109</v>
+        <v>0.097</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.257</v>
+        <v>0.236</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>0</v>
@@ -3190,28 +3190,28 @@
         <v>0</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.962</v>
+        <v>0.614</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.038</v>
+        <v>0.386</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.343</v>
+        <v>0.001</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.82</v>
+        <v>0.193</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>0</v>
@@ -3251,28 +3251,28 @@
         <v>0</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>0.667</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.745</v>
+        <v>0.762</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.255</v>
+        <v>0.238</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.074</v>
+        <v>0.111</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.338</v>
+        <v>0.377</v>
       </c>
       <c r="M33" s="6" t="n">
         <v>0</v>
@@ -3312,28 +3312,28 @@
         <v>0</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.912</v>
+        <v>0.85</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.058</v>
+        <v>0.008</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.241</v>
+        <v>0.089</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.625</v>
+        <v>0.448</v>
       </c>
       <c r="M34" s="4" t="n">
         <v>0</v>
@@ -3376,25 +3376,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.611</v>
+        <v>0.672</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.389</v>
+        <v>0.328</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.062</v>
+        <v>0.014</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.229</v>
+        <v>0.204</v>
       </c>
       <c r="M35" s="6" t="n">
         <v>0</v>
@@ -3434,28 +3434,28 @@
         <v>0</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.96</v>
+        <v>0.519</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.481</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>0.274</v>
+        <v>0</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="M36" s="4" t="n">
         <v>0</v>
@@ -3501,10 +3501,10 @@
         <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.455</v>
+        <v>0.239</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.546</v>
+        <v>0.761</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
@@ -3513,10 +3513,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.083</v>
+        <v>0.013</v>
       </c>
       <c r="M37" s="6" t="n">
         <v>0</v>
@@ -3556,28 +3556,28 @@
         <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.778</v>
+        <v>0.534</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.222</v>
+        <v>0.466</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K38" s="4" t="n">
         <v>0.046</v>
       </c>
-      <c r="K38" s="4" t="n">
-        <v>0.145</v>
-      </c>
       <c r="L38" s="4" t="n">
-        <v>0.408</v>
+        <v>0.194</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>0</v>
@@ -3620,25 +3620,25 @@
         <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.775</v>
+        <v>0.503</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.225</v>
+        <v>0.497</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.3</v>
+        <v>0.067</v>
       </c>
       <c r="M39" s="6" t="n">
         <v>0</v>
@@ -3675,31 +3675,31 @@
         <v>0</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.491</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.509</v>
+        <v>0.06</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.199</v>
+        <v>0.329</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.316</v>
+        <v>0.487</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.429</v>
+        <v>0.748</v>
       </c>
       <c r="M40" s="4" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.243</v>
+        <v>0.47</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.757</v>
+        <v>0.53</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
@@ -3757,10 +3757,10 @@
         <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.018</v>
+        <v>0.068</v>
       </c>
       <c r="M41" s="6" t="n">
         <v>0</v>
@@ -3800,28 +3800,28 @@
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.92</v>
+        <v>0.662</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.08</v>
+        <v>0.338</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.275</v>
+        <v>0.004</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.652</v>
+        <v>0.163</v>
       </c>
       <c r="M42" s="4" t="n">
         <v>0</v>
@@ -3867,10 +3867,10 @@
         <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.433</v>
+        <v>0.312</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0</v>
@@ -3879,10 +3879,10 @@
         <v>0</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.103</v>
+        <v>0.03</v>
       </c>
       <c r="M43" s="6" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.576</v>
+        <v>0.599</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.424</v>
+        <v>0.401</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>0</v>
@@ -3940,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.138</v>
+        <v>0.156</v>
       </c>
       <c r="M44" s="4" t="n">
         <v>0</v>
@@ -3986,13 +3986,13 @@
         <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.631</v>
+        <v>0.381</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.369</v>
+        <v>0.619</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
@@ -4001,10 +4001,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.177</v>
+        <v>0.065</v>
       </c>
       <c r="M45" s="6" t="n">
         <v>0</v>
@@ -4044,28 +4044,28 @@
         <v>0</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.655</v>
+        <v>0.858</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.345</v>
+        <v>0.142</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.014</v>
+        <v>0.104</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.082</v>
+        <v>0.239</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.296</v>
+        <v>0.528</v>
       </c>
       <c r="M46" s="4" t="n">
         <v>0</v>
@@ -4105,28 +4105,28 @@
         <v>0</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.286</v>
+        <v>0.429</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.492</v>
+        <v>0.449</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.508</v>
+        <v>0.551</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.061</v>
+        <v>0.041</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.187</v>
+        <v>0.189</v>
       </c>
       <c r="M47" s="6" t="n">
         <v>0</v>
@@ -4163,31 +4163,31 @@
         <v>0</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.507</v>
+        <v>0.994</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.493</v>
+        <v>0.006</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0</v>
+        <v>0.823</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>0.907</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.968</v>
       </c>
       <c r="M48" s="4" t="n">
         <v>0</v>
@@ -4230,25 +4230,25 @@
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.609</v>
+        <v>0.438</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.391</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.038</v>
+        <v>0.002</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.229</v>
+        <v>0.083</v>
       </c>
       <c r="M49" s="6" t="n">
         <v>0</v>
